--- a/demo.xlsx
+++ b/demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="18105" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>LoginSales</t>
+  </si>
   <si>
     <t>Incoterm</t>
   </si>
@@ -50,6 +53,21 @@
     <t>Unit</t>
   </si>
   <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Is End User</t>
+  </si>
+  <si>
+    <t>Sell From</t>
+  </si>
+  <si>
+    <t>Yard Address</t>
+  </si>
+  <si>
+    <t>Anson Ni</t>
+  </si>
+  <si>
     <t>DDP</t>
   </si>
   <si>
@@ -66,6 +84,15 @@
   </si>
   <si>
     <t>ft</t>
+  </si>
+  <si>
+    <t>Precise Pipe</t>
+  </si>
+  <si>
+    <t>Precise Pipe Inc.</t>
+  </si>
+  <si>
+    <t>2155 University Ave, Bronx, NY 10453, USA</t>
   </si>
   <si>
     <t xml:space="preserve">NPS 1/8 XS </t>
@@ -705,15 +732,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1246,15 +1270,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="34.25" customWidth="1"/>
+    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="32.375" customWidth="1"/>
+    <col min="6" max="6" width="34.25" customWidth="1"/>
+    <col min="9" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="17.875" customWidth="1"/>
+    <col min="12" max="12" width="44.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1276,70 +1304,100 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2">
         <v>100</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:7">
-      <c r="D3" s="2"/>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3">
-        <v>120</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
+    <row r="3" ht="15" customHeight="1" spans="1:12">
+      <c r="E3" s="2"/>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="2">
+        <v>200</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2">
-        <v>100</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
+    <row r="4" spans="1:12">
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2">
+        <v>300</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="D5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2"/>
+    <row r="5" spans="1:12">
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
